--- a/Result/profitability/1776.xlsx
+++ b/Result/profitability/1776.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2575000000000001</v>
+        <v>0.2675</v>
       </c>
       <c r="N2" t="n">
-        <v>17.85125</v>
+        <v>18.46375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3</v>
+        <v>0.3225</v>
       </c>
       <c r="N3" t="n">
-        <v>17.21</v>
+        <v>17.64625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.76</v>
       </c>
       <c r="M4" t="n">
-        <v>0.50375</v>
+        <v>0.525</v>
       </c>
       <c r="N4" t="n">
-        <v>17.69</v>
+        <v>18.61625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.77</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7075</v>
+        <v>0.76125</v>
       </c>
       <c r="N5" t="n">
-        <v>18.4025</v>
+        <v>19.66625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>98.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>1.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8500000000000001</v>
+        <v>0.88625</v>
       </c>
       <c r="N6" t="n">
-        <v>18.80875</v>
+        <v>19.13125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.26</v>
       </c>
       <c r="M7" t="n">
-        <v>1.005</v>
+        <v>1.015</v>
       </c>
       <c r="N7" t="n">
-        <v>18.42</v>
+        <v>18.41875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8179,6 +8179,133 @@
       </c>
       <c r="AM61" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1776</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>253</v>
+      </c>
+      <c r="D62" t="n">
+        <v>196</v>
+      </c>
+      <c r="E62" t="n">
+        <v>57</v>
+      </c>
+      <c r="F62" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="G62" t="n">
+        <v>20</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>7.75%</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>8</v>
+      </c>
+      <c r="J62" t="n">
+        <v>27</v>
+      </c>
+      <c r="K62" t="n">
+        <v>18</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.16125</v>
+      </c>
+      <c r="N62" t="n">
+        <v>19.00375</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-0.03999999999999998</v>
+      </c>
+      <c r="X62" t="n">
+        <v>-0.1142857142857142</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-0.5899999999999999</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-0.02556325823223571</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>-3.583333333333333</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.8166397415185782</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK62" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
